--- a/Electricals/Pinouts/LattePanda_Mu_Edge_Connector_Pinout.xlsx
+++ b/Electricals/Pinouts/LattePanda_Mu_Edge_Connector_Pinout.xlsx
@@ -149,7 +149,7 @@
     <t>System Power Supply Status</t>
   </si>
   <si>
-    <t>Output HIGH only when S0(Working)</t>
+    <t>Output HIGH only when S0(Working); 10K Pull-up to 3.3V (Weak Drive of HIGH output)</t>
   </si>
   <si>
     <t>SLP_S4</t>
@@ -741,7 +741,7 @@
     <t>CPU Fan Tacho</t>
   </si>
   <si>
-    <t>TAN3_CTL</t>
+    <t>FAN3_CTL</t>
   </si>
   <si>
     <t>SYS Fan PWM</t>
@@ -2577,11 +2577,11 @@
   <cols>
     <col min="1" max="1" width="4.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.2583333333333" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="61.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="50.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="50.2583333333333" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -5435,9 +5435,9 @@
   <dimension ref="A1:G132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.75833333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="24.9" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.7583333333333" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="61.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="10.625" style="2" customWidth="1"/>
